--- a/results/job_matches_2026-09-29.xlsx
+++ b/results/job_matches_2026-09-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - West Region</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Data Factory, Databricks, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a19bfa35530d300</t>
+          <t>https://www.indeed.com/viewjob?jk=e85738fcb60fb623</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Data Factory, Databricks, GCP, BigQuery, Spark</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85738fcb60fb623</t>
+          <t>https://www.indeed.com/viewjob?jk=57561f036d84d300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Gama-1 Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57561f036d84d300</t>
+          <t>https://www.indeed.com/viewjob?jk=eb56568b0a34217f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Python &amp; Java Full Stack Developer (AI-Assisted)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gama-1 Technologies</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Spark</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb56568b0a34217f</t>
+          <t>https://www.indeed.com/viewjob?jk=65877c8eb122e7ac</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271619709a30cff7</t>
+          <t>https://www.indeed.com/viewjob?jk=b54c7cf7e0d49278</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Technology Consultant - Cloud &amp; Full Stack Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Spark, Scala, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f10e71883167c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=73b249b48cff4978</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Full Stack developer-5</t>
+          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40bc09f1a3bfee6</t>
+          <t>https://www.indeed.com/viewjob?jk=271619709a30cff7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Full Stack developer-5</t>
+          <t>Full-stack Engineer 4 (Distributed data &amp; AWS) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5be589ee17517c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f43423f60faa323d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Full Stack developer-5</t>
+          <t>Technology Consultant - Cloud &amp; Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Spark, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4e07503808394b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f10e71883167c5f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GreatAmerica Financial Services</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5c22ff1e61705f</t>
+          <t>https://www.indeed.com/viewjob?jk=51a31aef3876037c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>GreatAmerica Financial Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e0f177f03aebbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=de5c22ff1e61705f</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78ec447c6921557</t>
+          <t>https://www.indeed.com/viewjob?jk=5e0f177f03aebbc1</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d121867f08ee42</t>
+          <t>https://www.indeed.com/viewjob?jk=e78ec447c6921557</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd3cf170c956d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=34d121867f08ee42</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c8ce709821c415</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd3cf170c956d7d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1850028e14e4bff5</t>
+          <t>https://www.indeed.com/viewjob?jk=12c8ce709821c415</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, API Gateway, IAM, Databricks, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aaa9ea40857cff1</t>
+          <t>https://www.indeed.com/viewjob?jk=1850028e14e4bff5</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>EMR, Kinesis, Athena, RDS, Hadoop, Scala, Kafka, Snowflake, Oracle, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff8cf7c0caa031</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ed04a9d166985</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b433e5c3de97183c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff8cf7c0caa031</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2abd9312c38916a</t>
+          <t>https://www.indeed.com/viewjob?jk=b433e5c3de97183c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c9fe751059a090</t>
+          <t>https://www.indeed.com/viewjob?jk=e2abd9312c38916a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519ba6eb81f01ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=54c9fe751059a090</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e9b1f872b9ca87</t>
+          <t>https://www.indeed.com/viewjob?jk=519ba6eb81f01ddd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b6f2a27bb5dca4</t>
+          <t>https://www.indeed.com/viewjob?jk=02e9b1f872b9ca87</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III: Backend C#</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,52 +1431,52 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc6bd5f5982957</t>
+          <t>https://www.indeed.com/viewjob?jk=88b6f2a27bb5dca4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III: Backend C#</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b919203f949fd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc6bd5f5982957</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0601bfbb6c8f14</t>
+          <t>https://www.indeed.com/viewjob?jk=9b919203f949fd3f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Reference Data Engineer New</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7000b43a0fcbe29</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0601bfbb6c8f14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) Architect - OI State Government Solutions - Remote</t>
+          <t>Databricks Engineer - Contractor (contract)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e53d9ca8bf12e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f788a895458b3b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer - Cloud Infrastructure, Thrivent Asset Management</t>
+          <t>Enterprise Data Warehouse (EDW) Architect - OI State Government Solutions - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ff30d29fb994c6</t>
+          <t>https://www.indeed.com/viewjob?jk=89e53d9ca8bf12e1</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Step Functions, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693264dcdef8b708</t>
+          <t>https://www.indeed.com/viewjob?jk=dba066468e1bd0ab</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Platform Site Reliability Engineer</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>First Due</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3d5d7e53a35fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1fbedd6c9d0d1c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50028acce61fae20</t>
+          <t>https://www.indeed.com/viewjob?jk=519dcdfdfb4bef2a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f22a963618e371</t>
+          <t>https://www.indeed.com/viewjob?jk=de1d075b9f067a1b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python</t>
+          <t>Senior Engineer - Cloud Infrastructure, Thrivent Asset Management</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae70768d6fa1ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=84ff30d29fb994c6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Consultant/Senior Consultant - (US-CENTRAL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df197bbb6fa7ca32</t>
+          <t>https://www.indeed.com/viewjob?jk=693264dcdef8b708</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Azure DevOps and SRE Engineer</t>
+          <t>Platform Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Berlin Packaging</t>
+          <t>First Due</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9b4b58bac9acaa</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3d5d7e53a35fd9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Distributed Systems Engineer, Energy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, DynamoDB, NoSQL, CI/CD, AWS CodePipeline, Terraform</t>
+          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b38e86282fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5a63e864705cad81</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78144b16700d5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=50028acce61fae20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer/AI Solution Engineer</t>
+          <t>Salesforce Developer with python</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Elkton, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7a8b75d558d86a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f22a963618e371</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate, Data &amp; Technology</t>
+          <t>Salesforce Developer with python</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, IAM, RDS, Scala, Snowflake, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c48bf8c53a131</t>
+          <t>https://www.indeed.com/viewjob?jk=fae70768d6fa1ea0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638b097bc0875ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbf885ed4904a21</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b98cfef06d7bc8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=e44d3b7e0c07709d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Advanced AI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Relativity</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad0487fcf429038</t>
+          <t>https://www.indeed.com/viewjob?jk=423eda1e0efbb045</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, DynamoDB, NoSQL, CI/CD, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41557f01cc587703</t>
+          <t>https://www.indeed.com/viewjob?jk=85b38e86282fc1ef</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9993c511c47797c</t>
+          <t>https://www.indeed.com/viewjob?jk=f78144b16700d5b2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - App Experience</t>
+          <t>Database Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HiveWatch</t>
+          <t>Esimplicity</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hive, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Oracle, Fact Tables, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9778ba4147d2ed02</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b1dfc73fb156e2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Data Engineer/AI Solution Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Elkton, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a8ea27729acb82</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7a8b75d558d86a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Kalamazoo, MI</t>
+          <t>Associate, Data &amp; Technology</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Greenleaf Trust</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Athena, S3, SNS, IAM, RDS, Scala, Snowflake, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b7f499e3abfee3</t>
+          <t>https://www.indeed.com/viewjob?jk=125c48bf8c53a131</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL, ELT</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724b45955d615a29</t>
+          <t>https://www.indeed.com/viewjob?jk=638b097bc0875ea2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1bec11137219f0</t>
+          <t>https://www.indeed.com/viewjob?jk=b98cfef06d7bc8c4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2f25853b8a0412</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad0487fcf429038</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd474395c7b916</t>
+          <t>https://www.indeed.com/viewjob?jk=41557f01cc587703</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5d12e525fc0c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=76c080f60278d6dc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Junior Data Security Engineer</t>
+          <t>Sr. Full-Stack/API Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>DSFederal, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,102 +2491,102 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0231b5b6e9bb14</t>
+          <t>https://www.indeed.com/viewjob?jk=1933ec0e840c5e53</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fadd67c5d6b60a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9993c511c47797c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Full Stack Engineer - App Experience</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>HiveWatch</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Hive, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b982bc2ef3815e44</t>
+          <t>https://www.indeed.com/viewjob?jk=9778ba4147d2ed02</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>RightsLine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63bbe79a14f6024</t>
+          <t>https://www.indeed.com/viewjob?jk=355bd600a0ce4716</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=575d748548b1953f</t>
+          <t>https://www.indeed.com/viewjob?jk=99a8ea27729acb82</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake, MySQL, Python)</t>
+          <t>Data Engineer - Kalamazoo, MI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Greenleaf Trust</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Covington, KY, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MySQL, ETL, ELT, Tableau, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f268439e97b6e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=82b7f499e3abfee3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blackpoint Cyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a7e3434ede4595</t>
+          <t>https://www.indeed.com/viewjob?jk=724b45955d615a29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,15 +2718,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, S3, RDS, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e18497d5c7efef</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1bec11137219f0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Columbia Sportswear</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Snowflake, SQL Server, Data Modeling, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bccfa443129fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2f25853b8a0412</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect and Integration Specialist</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f898ef3036623e7</t>
+          <t>https://www.indeed.com/viewjob?jk=02cd474395c7b916</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior SW Engineer, AI Automation</t>
+          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dentsply Sirona</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3794a67a181956</t>
+          <t>https://www.indeed.com/viewjob?jk=c27a0b23fadd4e76</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f00ff6ed18dfd67</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fadd67c5d6b60a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Faegre Drinker Biddle &amp; Reath LLP</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdb0c320e9d6d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b982bc2ef3815e44</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Oracle, PostgreSQL, Power BI, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd0e00d31627020</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5d12e525fc0c4f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer PA2026Q3JB011</t>
+          <t>Junior Data Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b6663fd8d25645</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0231b5b6e9bb14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efab3b52406bee28</t>
+          <t>https://www.indeed.com/viewjob?jk=b63bbe79a14f6024</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f966e76c6499fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=575d748548b1953f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Snowflake, MySQL, Python)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Covington, KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MySQL, ETL, ELT, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c44e30d78a1e64</t>
+          <t>https://www.indeed.com/viewjob?jk=3f268439e97b6e1b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Taskrabbit</t>
+          <t>Blackpoint Cyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7814dca29175e0</t>
+          <t>https://www.indeed.com/viewjob?jk=49a7e3434ede4595</t>
         </is>
       </c>
     </row>
@@ -3133,55 +3133,55 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Scala, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02c0599e49eb558</t>
+          <t>https://www.indeed.com/viewjob?jk=17e18497d5c7efef</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Columbia Sportswear</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>ECS, RDS, Azure, Snowflake, SQL Server, Data Modeling, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5989aaf1c5b0e5be</t>
+          <t>https://www.indeed.com/viewjob?jk=80bccfa443129fc3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Architect and Integration Specialist</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d0f6d172140e24</t>
+          <t>https://www.indeed.com/viewjob?jk=4f898ef3036623e7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb55e308f3bed84</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7223f2600dffbd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Senior SW Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Dentsply Sirona</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ae5f57c116bd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3794a67a181956</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>IT Supervisor Data &amp; Operations</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VIVA Railings LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38100b2f7e3761e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a96f65d48d365cdb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Faegre Drinker Biddle &amp; Reath LLP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae4a1fb3a4e5486</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdb0c320e9d6d0e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, S3, RDS, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86f759344da5731</t>
+          <t>https://www.indeed.com/viewjob?jk=1f00ff6ed18dfd67</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Taylor, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Scala, Oracle, PostgreSQL, Power BI, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5792d86986aeaceb</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd0e00d31627020</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer PA2026Q3JB011</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780fb85d3fe176eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b6663fd8d25645</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045d792db134b78e</t>
+          <t>https://www.indeed.com/viewjob?jk=efab3b52406bee28</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c13406c81164399</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b43cbdd72bcba2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=168c9d8374ad2930</t>
+          <t>https://www.indeed.com/viewjob?jk=508764c031e252bf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Maximo</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=810c7c9aefe11f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=57a51ee9cdac73f1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Entry-Level Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58901101639dcbfa</t>
+          <t>https://www.indeed.com/viewjob?jk=4514ecc84233be42</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Operations Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EDM Lead Network</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, GitHub Actions, Terraform, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,42 +3681,1197 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b73505b55ece80fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9551dd95afdb1040</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Financial Risk Analytics Engineer</t>
+          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openbank Deutschland AG</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f67c359ae426c4af</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19873039025aa3c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Go, Python, Java)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29aaf0f8edda59ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3f599d1a2697280</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f1e11573274ef49</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b3c11f0e138eb84</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7374c6749391f2ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Python, Java, Spring Boot)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1f77940dd9eb1d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Go &amp; Kubernetes) (Enterprise Platforms Technology)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0553ca4bc8ebe65</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32c94f784d741229</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 - AML Reporting</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ac04783f1f20e72</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Backend &amp; API Development) (Cloud Operations Resilience Engineering)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Riverwoods, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94ef24bdc8f0aec2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Cornell University</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ithaca, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f966e76c6499fe1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>KBX</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Green Bay, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d82ffb5eaa627d9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>KBX</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6e7dd4a9a7ed2c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Taskrabbit</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, dbt, Tableau, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c7814dca29175e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MHK TECH</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Malvern, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Scala, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d02c0599e49eb558</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; Platform</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d283def45f7dc44</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5989aaf1c5b0e5be</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46d0f6d172140e24</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Consultant or Senior Consultant, Technical Solutions</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>AVP, Inc.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cf1c610c653b6b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae4a1fb3a4e5486</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d86f759344da5731</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5792d86986aeaceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>Boston, MA, US USA</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D118" t="n">
         <v>10.4</v>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, Tableau, CI/CD, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4df4a2a841265604</t>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=780fb85d3fe176eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=045d792db134b78e</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c13406c81164399</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38100b2f7e3761e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bb55e308f3bed84</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7ae5f57c116bd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=168c9d8374ad2930</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Entry-Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Benda Infotech</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58901101639dcbfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EDM Lead Network</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, GitHub Actions, Terraform, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b73505b55ece80fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Maximo</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>National Grid</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=810c7c9aefe11f4c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-29.xlsx
+++ b/results/job_matches_2026-09-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>MSONE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Data Factory, Databricks, GCP, BigQuery, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85738fcb60fb623</t>
+          <t>https://www.indeed.com/viewjob?jk=f40077ff206f8543</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Data Factory, Databricks, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57561f036d84d300</t>
+          <t>https://www.indeed.com/viewjob?jk=e85738fcb60fb623</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gama-1 Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Spark</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb56568b0a34217f</t>
+          <t>https://www.indeed.com/viewjob?jk=57561f036d84d300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python &amp; Java Full Stack Developer (AI-Assisted)</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Gama-1 Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65877c8eb122e7ac</t>
+          <t>https://www.indeed.com/viewjob?jk=eb56568b0a34217f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python &amp; Java Full Stack Developer (AI-Assisted)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Trisura Guarantee Insurance Company</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541b5d8a70246d22</t>
+          <t>https://www.indeed.com/viewjob?jk=65877c8eb122e7ac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Heart Association</t>
+          <t>Trisura Guarantee Insurance Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Hadoop</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25ffbb13cf2cded</t>
+          <t>https://www.indeed.com/viewjob?jk=541b5d8a70246d22</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, SQL Server, MongoDB</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a31aef3876037c</t>
+          <t>https://www.indeed.com/viewjob?jk=8150f9e8b835ffb3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GreatAmerica Financial Services</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5c22ff1e61705f</t>
+          <t>https://www.indeed.com/viewjob?jk=51a31aef3876037c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>GreatAmerica Financial Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e0f177f03aebbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=de5c22ff1e61705f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
+          <t>EMR, Kinesis, Athena, RDS, Hadoop, Scala, Kafka, Snowflake, Oracle, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78ec447c6921557</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ed04a9d166985</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Bollinger Shipyards</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raceland, LA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d121867f08ee42</t>
+          <t>https://www.indeed.com/viewjob?jk=664254325a625205</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd3cf170c956d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ea6449546ca7a9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
+          <t>Senior Solutions Architect, Pre-sales | Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12c8ce709821c415</t>
+          <t>https://www.indeed.com/viewjob?jk=0540b2761589d7f9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Data Analytics &amp; BI</t>
+          <t>Software Engineer III: Backend C#</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1850028e14e4bff5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9180a14620aa14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III: Backend C#</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EMR, Kinesis, Athena, RDS, Hadoop, Scala, Kafka, Snowflake, Oracle, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ed04a9d166985</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc6bd5f5982957</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff8cf7c0caa031</t>
+          <t>https://www.indeed.com/viewjob?jk=88b6f2a27bb5dca4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b433e5c3de97183c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b919203f949fd3f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2abd9312c38916a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0601bfbb6c8f14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Engineer - Contractor (contract)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c9fe751059a090</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f788a895458b3b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Architect Wealth And Retirement</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Bridgenext</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Event Hubs, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519ba6eb81f01ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=4cbdbb96af073d71</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Warehouse (EDW) Architect - OI State Government Solutions - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e9b1f872b9ca87</t>
+          <t>https://www.indeed.com/viewjob?jk=89e53d9ca8bf12e1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>System Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Unify Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Hazelwood, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>Lambda, S3, ECS, IAM, RDS, PostgreSQL, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b6f2a27bb5dca4</t>
+          <t>https://www.indeed.com/viewjob?jk=050a71947c15c731</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III: Backend C#</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc6bd5f5982957</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5355e15b9a9081</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Medpace</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b919203f949fd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d80e20e6c49d29b</t>
         </is>
       </c>
     </row>
@@ -1523,20 +1523,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Step Functions, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0601bfbb6c8f14</t>
+          <t>https://www.indeed.com/viewjob?jk=dba066468e1bd0ab</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Databricks Engineer - Contractor (contract)</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f788a895458b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1fbedd6c9d0d1c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) Architect - OI State Government Solutions - Remote</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e53d9ca8bf12e1</t>
+          <t>https://www.indeed.com/viewjob?jk=519dcdfdfb4bef2a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba066468e1bd0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=de1d075b9f067a1b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>Senior Engineer - Cloud Infrastructure, Thrivent Asset Management</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1fbedd6c9d0d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=84ff30d29fb994c6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519dcdfdfb4bef2a</t>
+          <t>https://www.indeed.com/viewjob?jk=693264dcdef8b708</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>Distributed Systems Engineer, Energy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1d075b9f067a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a63e864705cad81</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer - Cloud Infrastructure, Thrivent Asset Management</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ff30d29fb994c6</t>
+          <t>https://www.indeed.com/viewjob?jk=50028acce61fae20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Developer with python</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693264dcdef8b708</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f22a963618e371</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Platform Site Reliability Engineer</t>
+          <t>Salesforce Developer with python</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>First Due</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3d5d7e53a35fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=fae70768d6fa1ea0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Distributed Systems Engineer, Energy</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a63e864705cad81</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbf885ed4904a21</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50028acce61fae20</t>
+          <t>https://www.indeed.com/viewjob?jk=e44d3b7e0c07709d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python</t>
+          <t>Advanced AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Relativity</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+          <t>AWS, EMR, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f22a963618e371</t>
+          <t>https://www.indeed.com/viewjob?jk=423eda1e0efbb045</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, DynamoDB, NoSQL, CI/CD, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae70768d6fa1ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=85b38e86282fc1ef</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Data Engineer Remote - w2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>itheroes inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbf885ed4904a21</t>
+          <t>https://www.indeed.com/viewjob?jk=f78144b16700d5b2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Database Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Esimplicity</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Oracle, Fact Tables, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e44d3b7e0c07709d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b1dfc73fb156e2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer</t>
+          <t>Data Engineer/AI Solution Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Relativity</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Elkton, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423eda1e0efbb045</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7a8b75d558d86a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Associate, Data &amp; Technology</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, DynamoDB, NoSQL, CI/CD, AWS CodePipeline, Terraform</t>
+          <t>AWS, Athena, S3, SNS, IAM, RDS, Scala, Snowflake, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b38e86282fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=125c48bf8c53a131</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78144b16700d5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=638b097bc0875ea2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Database Engineer III</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Esimplicity</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Oracle, Fact Tables, Amazon QuickSight, Power BI</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b1dfc73fb156e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b98cfef06d7bc8c4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer/AI Solution Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Elkton, MD, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7a8b75d558d86a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad0487fcf429038</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate, Data &amp; Technology</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, IAM, RDS, Scala, Snowflake, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c48bf8c53a131</t>
+          <t>https://www.indeed.com/viewjob?jk=41557f01cc587703</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638b097bc0875ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=76c080f60278d6dc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>RightsLine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b98cfef06d7bc8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=355bd600a0ce4716</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Sr. Full-Stack/API Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>DSFederal, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad0487fcf429038</t>
+          <t>https://www.indeed.com/viewjob?jk=1933ec0e840c5e53</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41557f01cc587703</t>
+          <t>https://www.indeed.com/viewjob?jk=a9993c511c47797c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - AWS Infrastructure &amp; Platform</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c080f60278d6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=99a8ea27729acb82</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack/API Developer</t>
+          <t>Data Engineer I - Data Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DSFederal, Inc.</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1933ec0e840c5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=b7daae54db1e425f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9993c511c47797c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6d0a91a10a1715</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - App Experience</t>
+          <t>Data Engineer - Kalamazoo, MI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HiveWatch</t>
+          <t>Greenleaf Trust</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hive, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9778ba4147d2ed02</t>
+          <t>https://www.indeed.com/viewjob?jk=82b7f499e3abfee3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RightsLine</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, NoSQL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355bd600a0ce4716</t>
+          <t>https://www.indeed.com/viewjob?jk=724b45955d615a29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, S3, RDS, Spark, PySpark, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a8ea27729acb82</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1bec11137219f0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Kalamazoo, MI</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Greenleaf Trust</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b7f499e3abfee3</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2f25853b8a0412</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL, ELT</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724b45955d615a29</t>
+          <t>https://www.indeed.com/viewjob?jk=02cd474395c7b916</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1bec11137219f0</t>
+          <t>https://www.indeed.com/viewjob?jk=b87121ab466a00f3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2f25853b8a0412</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5d12e525fc0c4f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd474395c7b916</t>
+          <t>https://www.indeed.com/viewjob?jk=b982bc2ef3815e44</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
+          <t>Junior Data Security Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27a0b23fadd4e76</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0231b5b6e9bb14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fadd67c5d6b60a</t>
+          <t>https://www.indeed.com/viewjob?jk=b63bbe79a14f6024</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b982bc2ef3815e44</t>
+          <t>https://www.indeed.com/viewjob?jk=575d748548b1953f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Blackpoint Cyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5d12e525fc0c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=49a7e3434ede4595</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Data Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, CI/CD</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0231b5b6e9bb14</t>
+          <t>https://www.indeed.com/viewjob?jk=17e18497d5c7efef</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63bbe79a14f6024</t>
+          <t>https://www.indeed.com/viewjob?jk=d194b726c3ec9477</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=575d748548b1953f</t>
+          <t>https://www.indeed.com/viewjob?jk=1f00ff6ed18dfd67</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake, MySQL, Python)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Covington, KY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MySQL, ETL, ELT, Tableau, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f268439e97b6e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7223f2600dffbd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior SW Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Blackpoint Cyber</t>
+          <t>Dentsply Sirona</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a7e3434ede4595</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3794a67a181956</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Faegre Drinker Biddle &amp; Reath LLP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e18497d5c7efef</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdb0c320e9d6d0e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer PA2026Q3JB011</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Columbia Sportswear</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Snowflake, SQL Server, Data Modeling, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bccfa443129fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b6663fd8d25645</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect and Integration Specialist</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Taylor, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Databricks, Scala, Oracle, PostgreSQL, Power BI, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f898ef3036623e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd0e00d31627020</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>IT Supervisor Data &amp; Operations</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>VIVA Railings LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7223f2600dffbd</t>
+          <t>https://www.indeed.com/viewjob?jk=a96f65d48d365cdb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior SW Engineer, AI Automation</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dentsply Sirona</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3794a67a181956</t>
+          <t>https://www.indeed.com/viewjob?jk=247c485b2435bbc9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IT Supervisor Data &amp; Operations</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VIVA Railings LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a96f65d48d365cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b43cbdd72bcba2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Faegre Drinker Biddle &amp; Reath LLP</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdb0c320e9d6d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=508764c031e252bf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f00ff6ed18dfd67</t>
+          <t>https://www.indeed.com/viewjob?jk=57a51ee9cdac73f1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Oracle, PostgreSQL, Power BI, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd0e00d31627020</t>
+          <t>https://www.indeed.com/viewjob?jk=4514ecc84233be42</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer PA2026Q3JB011</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b6663fd8d25645</t>
+          <t>https://www.indeed.com/viewjob?jk=9551dd95afdb1040</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
+          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efab3b52406bee28</t>
+          <t>https://www.indeed.com/viewjob?jk=f67c359ae426c4af</t>
         </is>
       </c>
     </row>
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b43cbdd72bcba2</t>
+          <t>https://www.indeed.com/viewjob?jk=19873039025aa3c2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full-stack Engineer 5 (Go, Python, Java)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508764c031e252bf</t>
+          <t>https://www.indeed.com/viewjob?jk=29aaf0f8edda59ec</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a51ee9cdac73f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f599d1a2697280</t>
         </is>
       </c>
     </row>
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4514ecc84233be42</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e11573274ef49</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9551dd95afdb1040</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3c11f0e138eb84</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67c359ae426c4af</t>
+          <t>https://www.indeed.com/viewjob?jk=7374c6749391f2ff</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Python, Java, Spring Boot)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19873039025aa3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f77940dd9eb1d5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Go, Python, Java)</t>
+          <t>Full-stack Engineer 4 (Go &amp; Kubernetes) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29aaf0f8edda59ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a0553ca4bc8ebe65</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f599d1a2697280</t>
+          <t>https://www.indeed.com/viewjob?jk=32c94f784d741229</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 - AML Reporting</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e11573274ef49</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac04783f1f20e72</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
+          <t>Full-stack Engineer 4 (Backend &amp; API Development) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3c11f0e138eb84</t>
+          <t>https://www.indeed.com/viewjob?jk=94ef24bdc8f0aec2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,102 +3926,102 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7374c6749391f2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4f966e76c6499fe1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Java, Spring Boot)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>KBX</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f77940dd9eb1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d82ffb5eaa627d9d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go &amp; Kubernetes) (Enterprise Platforms Technology)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>KBX</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0553ca4bc8ebe65</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e7dd4a9a7ed2c5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Taskrabbit</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,94 +4031,94 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c94f784d741229</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7814dca29175e0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 - AML Reporting</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>MHK TECH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Scala, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac04783f1f20e72</t>
+          <t>https://www.indeed.com/viewjob?jk=d02c0599e49eb558</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Backend &amp; API Development) (Cloud Operations Resilience Engineering)</t>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ef24bdc8f0aec2</t>
+          <t>https://www.indeed.com/viewjob?jk=9d283def45f7dc44</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f966e76c6499fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=5989aaf1c5b0e5be</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KBX</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82ffb5eaa627d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=46d0f6d172140e24</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KBX</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e7dd4a9a7ed2c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae4a1fb3a4e5486</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Taskrabbit</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, dbt, Tableau, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7814dca29175e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d86f759344da5731</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Scala, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02c0599e49eb558</t>
+          <t>https://www.indeed.com/viewjob?jk=5792d86986aeaceb</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Infrastructure &amp; Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d283def45f7dc44</t>
+          <t>https://www.indeed.com/viewjob?jk=780fb85d3fe176eb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5989aaf1c5b0e5be</t>
+          <t>https://www.indeed.com/viewjob?jk=045d792db134b78e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,19 +4381,19 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d0f6d172140e24</t>
+          <t>https://www.indeed.com/viewjob?jk=8c13406c81164399</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Consultant or Senior Consultant, Technical Solutions</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AVP, Inc.</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf1c610c653b6b3</t>
+          <t>https://www.indeed.com/viewjob?jk=168c9d8374ad2930</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae4a1fb3a4e5486</t>
+          <t>https://www.indeed.com/viewjob?jk=58901101639dcbfa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Operations Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>EDM Lead Network</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, GitHub Actions, Terraform, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86f759344da5731</t>
+          <t>https://www.indeed.com/viewjob?jk=b73505b55ece80fa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Maximo</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>National Grid</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5792d86986aeaceb</t>
+          <t>https://www.indeed.com/viewjob?jk=810c7c9aefe11f4c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780fb85d3fe176eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb55e308f3bed84</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045d792db134b78e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ae5f57c116bd7e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c13406c81164399</t>
+          <t>https://www.indeed.com/viewjob?jk=38100b2f7e3761e3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Consultant or Senior Consultant, Technical Solutions</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AVP, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,217 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38100b2f7e3761e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb55e308f3bed84</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ae5f57c116bd7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=168c9d8374ad2930</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Entry-Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Benda Infotech</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58901101639dcbfa</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>EDM Lead Network</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, GitHub Actions, Terraform, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b73505b55ece80fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Maximo</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>National Grid</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=810c7c9aefe11f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf1c610c653b6b3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-29.xlsx
+++ b/results/job_matches_2026-09-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,47 +508,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Cricut</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Data Factory, Databricks, GCP, BigQuery, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85738fcb60fb623</t>
+          <t>https://www.indeed.com/viewjob?jk=0116d4b4ca656c94</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Data Engineer - Apartments.com - Irvine, CA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57561f036d84d300</t>
+          <t>https://www.indeed.com/viewjob?jk=a53ace7c739bbef4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Data Engineer II - Apartments.com - Irvine, CA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gama-1 Technologies</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,29 +591,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Spark</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb56568b0a34217f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ca5cc30971dc02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python &amp; Java Full Stack Developer (AI-Assisted)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65877c8eb122e7ac</t>
+          <t>https://www.indeed.com/viewjob?jk=57561f036d84d300</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trisura Guarantee Insurance Company</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,59 +661,59 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541b5d8a70246d22</t>
+          <t>https://www.indeed.com/viewjob?jk=551c49c9aa5e5584</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SS&amp;C EVOLV</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1986790d4088685</t>
+          <t>https://www.indeed.com/viewjob?jk=660e2cf474b4e061</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,19 +736,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54c7cf7e0d49278</t>
+          <t>https://www.indeed.com/viewjob?jk=98b9323fde0e076c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b249b48cff4978</t>
+          <t>https://www.indeed.com/viewjob?jk=b54c7cf7e0d49278</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271619709a30cff7</t>
+          <t>https://www.indeed.com/viewjob?jk=73b249b48cff4978</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, BigQuery, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8150f9e8b835ffb3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d707249d6f4c2b1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>JACK'S</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, IAM, RDS, Google Cloud Platform, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a31aef3876037c</t>
+          <t>https://www.indeed.com/viewjob?jk=5920428f1dd8e6b7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GreatAmerica Financial Services</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5c22ff1e61705f</t>
+          <t>https://www.indeed.com/viewjob?jk=51a31aef3876037c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Southern Hobby Distribution</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EMR, Kinesis, Athena, RDS, Hadoop, Scala, Kafka, Snowflake, Oracle, DynamoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ed04a9d166985</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16d38559fc0b69</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Software Engineer - Pre-trade (Gas &amp; Power Industry)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bollinger Shipyards</t>
+          <t>Talan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raceland, LA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, Azure, Data Factory, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,94 +1056,94 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664254325a625205</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe858dfd726768d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>GreatAmerica Financial Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ea6449546ca7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=de5c22ff1e61705f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect, Pre-sales | Remote</t>
+          <t>C,C++, Python, Golang Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0540b2761589d7f9</t>
+          <t>https://www.indeed.com/viewjob?jk=adc654a7b5482d94</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III: Backend C#</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>EMR, Kinesis, Athena, RDS, Hadoop, Scala, Kafka, Snowflake, Oracle, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9180a14620aa14</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ed04a9d166985</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III: Backend C#</t>
+          <t>Data Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc6bd5f5982957</t>
+          <t>https://www.indeed.com/viewjob?jk=925e167443880f65</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Solutions Architect, Pre-sales | Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b6f2a27bb5dca4</t>
+          <t>https://www.indeed.com/viewjob?jk=0540b2761589d7f9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b919203f949fd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ea6449546ca7a9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Bollinger Shipyards</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raceland, LA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0601bfbb6c8f14</t>
+          <t>https://www.indeed.com/viewjob?jk=664254325a625205</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Engineer - Contractor (contract)</t>
+          <t>Software Engineer III: Backend C#</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,94 +1336,94 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f788a895458b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9180a14620aa14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Technical Architect Wealth And Retirement</t>
+          <t>Software Engineer III: Backend C#</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bridgenext</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Event Hubs, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cbdbb96af073d71</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc6bd5f5982957</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) Architect - OI State Government Solutions - Remote</t>
+          <t>Support &amp; Maintenance Engineer (L2/L3)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e53d9ca8bf12e1</t>
+          <t>https://www.indeed.com/viewjob?jk=94fcaf3be931931e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>System Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Unify Technologies</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hazelwood, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lambda, S3, ECS, IAM, RDS, PostgreSQL, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,207 +1441,207 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=050a71947c15c731</t>
+          <t>https://www.indeed.com/viewjob?jk=5dbffb9333bd2fe0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer - Contractor (contract)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5355e15b9a9081</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f788a895458b3b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Junior Business Intelligence Engineer</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Medpace</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d80e20e6c49d29b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f7e1ef8e1fdbe0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba066468e1bd0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=96d7c2108f3611f5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1fbedd6c9d0d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=a94392d03faa7aff</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519dcdfdfb4bef2a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a75acda2378a3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>Technical Architect Wealth And Retirement</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>Bridgenext</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Event Hubs, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1d075b9f067a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=4cbdbb96af073d71</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Engineer - Cloud Infrastructure, Thrivent Asset Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ff30d29fb994c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5355e15b9a9081</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693264dcdef8b708</t>
+          <t>https://www.indeed.com/viewjob?jk=c78e9f6e4739bce7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Distributed Systems Engineer, Energy</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a63e864705cad81</t>
+          <t>https://www.indeed.com/viewjob?jk=2a766168aef2c43f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50028acce61fae20</t>
+          <t>https://www.indeed.com/viewjob?jk=4d105c911a496d46</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f22a963618e371</t>
+          <t>https://www.indeed.com/viewjob?jk=9315f3e60bfa6075</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,182 +1851,182 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae70768d6fa1ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a0b6bcda04fafa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbf885ed4904a21</t>
+          <t>https://www.indeed.com/viewjob?jk=8645c5596f3bb194</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e44d3b7e0c07709d</t>
+          <t>https://www.indeed.com/viewjob?jk=f348d8dd12d13dc6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Relativity</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423eda1e0efbb045</t>
+          <t>https://www.indeed.com/viewjob?jk=85f353e2816c2a63</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, DynamoDB, NoSQL, CI/CD, AWS CodePipeline, Terraform</t>
+          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b38e86282fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6337d0b5fa6d92</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer Remote - w2</t>
+          <t>Junior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>itheroes inc</t>
+          <t>Medpace</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78144b16700d5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d80e20e6c49d29b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Database Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Esimplicity</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Oracle, Fact Tables, Amazon QuickSight, Power BI</t>
+          <t>AWS, Step Functions, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b1dfc73fb156e2</t>
+          <t>https://www.indeed.com/viewjob?jk=dba066468e1bd0ab</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer/AI Solution Engineer</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Elkton, MD, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7a8b75d558d86a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1fbedd6c9d0d1c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate, Data &amp; Technology</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, IAM, RDS, Scala, Snowflake, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c48bf8c53a131</t>
+          <t>https://www.indeed.com/viewjob?jk=519dcdfdfb4bef2a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638b097bc0875ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=de1d075b9f067a1b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Senior Engineer - Cloud Infrastructure, Thrivent Asset Management</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,94 +2211,94 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b98cfef06d7bc8c4</t>
+          <t>https://www.indeed.com/viewjob?jk=84ff30d29fb994c6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad0487fcf429038</t>
+          <t>https://www.indeed.com/viewjob?jk=0839459de9ce2dea</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Azure, Data Factory, Databricks, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41557f01cc587703</t>
+          <t>https://www.indeed.com/viewjob?jk=36e16b8afdb689b5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - AWS Infrastructure &amp; Platform</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c080f60278d6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbf885ed4904a21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RightsLine</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, NoSQL, dbt, Power BI</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355bd600a0ce4716</t>
+          <t>https://www.indeed.com/viewjob?jk=e44d3b7e0c07709d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack/API Developer</t>
+          <t>Advanced AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DSFederal, Inc.</t>
+          <t>Relativity</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1933ec0e840c5e53</t>
+          <t>https://www.indeed.com/viewjob?jk=423eda1e0efbb045</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, DynamoDB, NoSQL, CI/CD, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9993c511c47797c</t>
+          <t>https://www.indeed.com/viewjob?jk=85b38e86282fc1ef</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Database Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Esimplicity</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Oracle, Fact Tables, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a8ea27729acb82</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b1dfc73fb156e2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer I - Data Platform</t>
+          <t>Data Engineer/AI Solution Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Elkton, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7daae54db1e425f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7a8b75d558d86a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate, Data &amp; Technology</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau</t>
+          <t>AWS, Athena, S3, SNS, IAM, RDS, Scala, Snowflake, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a6d0a91a10a1715</t>
+          <t>https://www.indeed.com/viewjob?jk=125c48bf8c53a131</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Kalamazoo, MI</t>
+          <t>Data Architect – Global Information Security</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Greenleaf Trust</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b7f499e3abfee3</t>
+          <t>https://www.indeed.com/viewjob?jk=18a798b66406a564</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud Engineer</t>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724b45955d615a29</t>
+          <t>https://www.indeed.com/viewjob?jk=76c080f60278d6dc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Spark, PySpark, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1bec11137219f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a9993c511c47797c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Data Engineer I - Data Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2f25853b8a0412</t>
+          <t>https://www.indeed.com/viewjob?jk=b7daae54db1e425f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Senior Databricks Data Engineer (Chicago Area)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bilink Corp</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd474395c7b916</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc3f410679dfa32</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87121ab466a00f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6d0a91a10a1715</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5d12e525fc0c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f774f78f05e811f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Data Architect - Healthcare Insights, Revenue Cycle</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b982bc2ef3815e44</t>
+          <t>https://www.indeed.com/viewjob?jk=b58dd53022f160e8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Data Security Engineer</t>
+          <t>Data Architect - Healthcare Insights, Pharmacy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,217 +2831,217 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0231b5b6e9bb14</t>
+          <t>https://www.indeed.com/viewjob?jk=cae3580058d6b9fa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63bbe79a14f6024</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fcc3fc97e62735</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=575d748548b1953f</t>
+          <t>https://www.indeed.com/viewjob?jk=4849aac95d96923e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Blackpoint Cyber</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a7e3434ede4595</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d3746e241efd7b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e18497d5c7efef</t>
+          <t>https://www.indeed.com/viewjob?jk=5865d81e8fd72c5b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Dev Ops Engineer (SYS ADM 4 TX)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>UC Davis</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d194b726c3ec9477</t>
+          <t>https://www.indeed.com/viewjob?jk=a35d797a405aa8a0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f00ff6ed18dfd67</t>
+          <t>https://www.indeed.com/viewjob?jk=b87121ab466a00f3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Business Consultant - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Vertex AI, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7223f2600dffbd</t>
+          <t>https://www.indeed.com/viewjob?jk=b982bc2ef3815e44</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior SW Engineer, AI Automation</t>
+          <t>Full-Stack Engineer 4 (Nodejs, Angularjs, Java)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dentsply Sirona</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3794a67a181956</t>
+          <t>https://www.indeed.com/viewjob?jk=9b68e3f744cf85a2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Senior | Hybrid</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Faegre Drinker Biddle &amp; Reath LLP</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ELT, MLflow, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdb0c320e9d6d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e49db045a45c992</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer PA2026Q3JB011</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, IAM, RDS, Spark, SQL Server, dbt, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b6663fd8d25645</t>
+          <t>https://www.indeed.com/viewjob?jk=151ea1e60e7bac7b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Oracle, PostgreSQL, Power BI, CI/CD, GitHub Actions, Docker</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd0e00d31627020</t>
+          <t>https://www.indeed.com/viewjob?jk=b63bbe79a14f6024</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IT Supervisor Data &amp; Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VIVA Railings LLC</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a96f65d48d365cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=575d748548b1953f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Engineer, Technology I</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, IAM, MongoDB, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=247c485b2435bbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=a8e935360a6c84ae</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b43cbdd72bcba2</t>
+          <t>https://www.indeed.com/viewjob?jk=a8be491cf3beb6bb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Polars, MLflow, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508764c031e252bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aaff853ea9e0984e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Harrington Process Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chino, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a51ee9cdac73f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8614d77d4401e0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Harrington Process Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chino, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4514ecc84233be42</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0cad18cf1700f2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9551dd95afdb1040</t>
+          <t>https://www.indeed.com/viewjob?jk=d194b726c3ec9477</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67c359ae426c4af</t>
+          <t>https://www.indeed.com/viewjob?jk=1f00ff6ed18dfd67</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19873039025aa3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7223f2600dffbd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Go, Python, Java)</t>
+          <t>Senior SW Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Dentsply Sirona</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29aaf0f8edda59ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3794a67a181956</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cricut</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,24 +3601,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f599d1a2697280</t>
+          <t>https://www.indeed.com/viewjob?jk=6b81ccfe00621caf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Cyber)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3641,19 +3641,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e11573274ef49</t>
+          <t>https://www.indeed.com/viewjob?jk=50df5c630173a79e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
+          <t>Full-stack Engineer 5 (Cyber)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3c11f0e138eb84</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff744ea970f680d</t>
         </is>
       </c>
     </row>
@@ -3711,19 +3711,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7374c6749391f2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=544c5bd52b84d1f9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Java, Spring Boot)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3746,19 +3746,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f77940dd9eb1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=247c485b2435bbc9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go &amp; Kubernetes) (Enterprise Platforms Technology)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0553ca4bc8ebe65</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b43cbdd72bcba2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c94f784d741229</t>
+          <t>https://www.indeed.com/viewjob?jk=508764c031e252bf</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 - AML Reporting</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac04783f1f20e72</t>
+          <t>https://www.indeed.com/viewjob?jk=57a51ee9cdac73f1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Backend &amp; API Development) (Cloud Operations Resilience Engineering)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ef24bdc8f0aec2</t>
+          <t>https://www.indeed.com/viewjob?jk=4514ecc84233be42</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,102 +3926,102 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f966e76c6499fe1</t>
+          <t>https://www.indeed.com/viewjob?jk=9551dd95afdb1040</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KBX</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82ffb5eaa627d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=f67c359ae426c4af</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KBX</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e7dd4a9a7ed2c5</t>
+          <t>https://www.indeed.com/viewjob?jk=19873039025aa3c2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full-stack Engineer 5 (Go, Python, Java)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Taskrabbit</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,102 +4031,102 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7814dca29175e0</t>
+          <t>https://www.indeed.com/viewjob?jk=29aaf0f8edda59ec</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Scala, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02c0599e49eb558</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f599d1a2697280</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Infrastructure &amp; Platform</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d283def45f7dc44</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e11573274ef49</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5989aaf1c5b0e5be</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3c11f0e138eb84</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d0f6d172140e24</t>
+          <t>https://www.indeed.com/viewjob?jk=7374c6749391f2ff</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Python, Java, Spring Boot)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae4a1fb3a4e5486</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f77940dd9eb1d5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Go &amp; Kubernetes) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86f759344da5731</t>
+          <t>https://www.indeed.com/viewjob?jk=a0553ca4bc8ebe65</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5792d86986aeaceb</t>
+          <t>https://www.indeed.com/viewjob?jk=32c94f784d741229</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Engineer 4 - AML Reporting</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780fb85d3fe176eb</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac04783f1f20e72</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 (Backend &amp; API Development) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045d792db134b78e</t>
+          <t>https://www.indeed.com/viewjob?jk=94ef24bdc8f0aec2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Generative AI &amp; Healthcare Data)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Altarum</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c13406c81164399</t>
+          <t>https://www.indeed.com/viewjob?jk=1f49e9b26d98bb56</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Data Platform</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>UPLIGHT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, Databricks, Unity Catalog, GCP, Spark, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=168c9d8374ad2930</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb44c59e3216f7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Entry-Level Software Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58901101639dcbfa</t>
+          <t>https://www.indeed.com/viewjob?jk=990c95bc91fe1ded</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Operations Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EDM Lead Network</t>
+          <t>KBX</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, GitHub Actions, Terraform, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b73505b55ece80fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d82ffb5eaa627d9d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Maximo</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>KBX</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=810c7c9aefe11f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e7dd4a9a7ed2c5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>MHK TECH</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Scala, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb55e308f3bed84</t>
+          <t>https://www.indeed.com/viewjob?jk=d02c0599e49eb558</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ae5f57c116bd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2c19227b36b945</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38100b2f7e3761e3</t>
+          <t>https://www.indeed.com/viewjob?jk=04837ffb07121b8d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Consultant or Senior Consultant, Technical Solutions</t>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AVP, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,17 +4651,332 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf1c610c653b6b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9d283def45f7dc44</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d8da3c50569b80d</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae4a1fb3a4e5486</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d86f759344da5731</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5792d86986aeaceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=780fb85d3fe176eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=045d792db134b78e</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c13406c81164399</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5989aaf1c5b0e5be</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Maximo</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>National Grid</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=810c7c9aefe11f4c</t>
         </is>
       </c>
     </row>
